--- a/questionnaire_templates/045_self_discovery_questionnaire_template--questionnaire_templates.xlsx
+++ b/questionnaire_templates/045_self_discovery_questionnaire_template--questionnaire_templates.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
     <col width="47" customWidth="1" min="3" max="3"/>
     <col width="49" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -937,7 +937,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ideal Coach Coaching Style</t>
+          <t>Ideal Coach Coaching Style (2)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -955,12 +955,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ideal_coach_coaching_topics</t>
+          <t>ideal_coach_coaching_topics_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ideal Coach Coaching Topics</t>
+          <t>Ideal Coach Coaching Topics 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -978,12 +978,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ideal_coach_coaching_approaches</t>
+          <t>ideal_coach_coaching_approaches_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ideal Coach Coaching Approaches</t>
+          <t>Ideal Coach Coaching Approaches 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ideal_coach_coaching_methods</t>
+          <t>ideal_coach_coaching_methods_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ideal Coach Coaching Methods</t>
+          <t>Ideal Coach Coaching Methods 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ideal_coach_coaching_focus</t>
+          <t>ideal_coach_coaching_focus_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ideal Coach Coaching Focus</t>
+          <t>Ideal Coach Coaching Focus 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1047,12 +1047,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ideal_coach_coaching_style</t>
+          <t>ideal_coach_coaching_style_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ideal Coach Coaching Style</t>
+          <t>Ideal Coach Coaching Style (3)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ideal_coach_coaching_topics</t>
+          <t>ideal_coach_coaching_topics_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ideal Coach Coaching Topics</t>
+          <t>Ideal Coach Coaching Topics 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
